--- a/bills/JXZFSP/-5230747991/fb3be0ac56ee1c32672be87c290f01d6d775d30a3ececb38e220d2a50240a251/bill-2026-06-23.xlsx
+++ b/bills/JXZFSP/-5230747991/fb3be0ac56ee1c32672be87c290f01d6d775d30a3ececb38e220d2a50240a251/bill-2026-06-23.xlsx
@@ -164,94 +164,136 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>06/23 17:28:38</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>你直接看有没有车</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1111.11</t>
+          <t>9968</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1079.11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1111.11</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1079.11</t>
         </is>
       </c>
     </row>
